--- a/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
+++ b/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -461,66 +461,57 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cómo se sube</v>
+        <v>Archivos del módulo</v>
       </c>
       <c r="B4" t="str">
-        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+        <v>Este módulo lleva 2 archivos, cada uno en su propia carga del Centro de cargas: (1) "Llamadas" — Wolkvox, CDR (hoja "HistCDR&lt;fecha&gt;"). (2) "WhatsApp" — Wolkvox, HistChat (hoja "HistChat&lt;fecha&gt;"). Esta plantilla es la de "WhatsApp".</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Cómo se sube</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v>Importante</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B6" t="str">
         <v>No cambie los nombres de las columnas. Los ejemplos de abajo son inventados: no los copie a la hoja de datos.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Columna</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Obligatoria</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Qué va</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Ejemplo (inventado)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>También se acepta como</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AGENT_NAME</v>
+        <v>Columna</v>
       </c>
       <c r="B8" t="str">
-        <v>Sí</v>
+        <v>Obligatoria</v>
       </c>
       <c r="C8" t="str">
-        <v>Asesor.</v>
+        <v>Qué va</v>
       </c>
       <c r="D8" t="str">
-        <v>Asesor Ejemplo Uno</v>
+        <v>Ejemplo (inventado)</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>También se acepta como</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DATE</v>
+        <v>AGENT_NAME</v>
       </c>
       <c r="B9" t="str">
         <v>Sí</v>
       </c>
       <c r="C9" t="str">
-        <v>Fecha de la conversación.</v>
+        <v>Asesor.</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-08-01</v>
+        <v>Asesor Ejemplo Uno</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -528,16 +519,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>DESCRIPTION_COD_ACT</v>
+        <v>DATE</v>
       </c>
       <c r="B10" t="str">
         <v>Sí</v>
       </c>
       <c r="C10" t="str">
-        <v>Motivo o tipificación.</v>
+        <v>Fecha de la conversación.</v>
       </c>
       <c r="D10" t="str">
-        <v>Agendamiento</v>
+        <v>2026-08-01</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -545,24 +536,41 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>NOMBRE DE SKILL</v>
+        <v>DESCRIPTION_COD_ACT</v>
       </c>
       <c r="B11" t="str">
         <v>Sí</v>
       </c>
       <c r="C11" t="str">
+        <v>Motivo o tipificación.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Agendamiento</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>NOMBRE DE SKILL</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="C12" t="str">
         <v>Cola de WhatsApp ("NOMBRE DE SKILL" en el export).</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D12" t="str">
         <v>WHATSAPP GENERAL</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E12" t="str">
         <v>NOMBRE DE SKILL</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
+++ b/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
@@ -565,7 +565,7 @@
         <v>WHATSAPP GENERAL</v>
       </c>
       <c r="E12" t="str">
-        <v>NOMBRE DE SKILL</v>
+        <v>SKILL_NAME</v>
       </c>
     </row>
   </sheetData>

--- a/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
+++ b/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
@@ -398,12 +398,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -417,19 +418,22 @@
         <v>DESCRIPTION_COD_ACT</v>
       </c>
       <c r="D1" t="str">
-        <v>NOMBRE DE SKILL</v>
+        <v>SKILL_ID</v>
+      </c>
+      <c r="E1" t="str">
+        <v>CHANNEL</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -448,7 +452,7 @@
         <v>De dónde sale</v>
       </c>
       <c r="B2" t="str">
-        <v>Wolkvox: export "HistChat&lt;fecha&gt;". Se sube tal cual (no hay que renombrar la hoja); el sistema nunca lee nombres, correos, teléfonos ni el texto de las conversaciones.</v>
+        <v>Wolkvox: CDR de WhatsApp, export "HistChat&lt;fecha&gt;" — [ruta pendiente de confirmar con Edwin]. Se sube tal cual (no hay que renombrar la hoja); el sistema nunca lee nombres, correos, teléfonos ni el texto de las conversaciones. Un SKILL_ID que no esté en la tabla de skills se ignora y la vista previa dice cuántos.</v>
       </c>
     </row>
     <row r="3">
@@ -469,66 +473,57 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Cómo se sube</v>
+        <v>Skills de WhatsApp</v>
       </c>
       <c r="B5" t="str">
-        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+        <v>Tabla de skills de WhatsApp de ORLANT (SKILL_ID = nombre): 0 = WHATSAPP DE SALIDA; 4042 = WHATSAPP PAUTAS; 4047 = WHATSAPP AUDIFONOS; 4061 = WHATSAPP FONOAUDIOLOGIA; 4071 = WHATSAPP FONIATRIA; 4306 = WHATSAPP 3P; 4327 = WHATSAPP GENERAL; 4338 = WHATSAPP CONFIRMACIONES; 4362 = ATENCION TUTELAS. La edita un administrador en Cargar Datos → "Skills de WhatsApp".</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Cómo se sube</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>Importante</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B7" t="str">
         <v>No cambie los nombres de las columnas. Los ejemplos de abajo son inventados: no los copie a la hoja de datos.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Columna</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Obligatoria</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Qué va</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Ejemplo (inventado)</v>
-      </c>
-      <c r="E8" t="str">
-        <v>También se acepta como</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AGENT_NAME</v>
+        <v>Columna</v>
       </c>
       <c r="B9" t="str">
-        <v>Sí</v>
+        <v>Obligatoria</v>
       </c>
       <c r="C9" t="str">
-        <v>Asesor.</v>
+        <v>Qué va</v>
       </c>
       <c r="D9" t="str">
-        <v>Asesor Ejemplo Uno</v>
+        <v>Ejemplo (inventado)</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>También se acepta como</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>DATE</v>
+        <v>AGENT_NAME</v>
       </c>
       <c r="B10" t="str">
         <v>Sí</v>
       </c>
       <c r="C10" t="str">
-        <v>Fecha de la conversación.</v>
+        <v>Asesor.</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-08-01</v>
+        <v>Asesor Ejemplo Uno</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -536,16 +531,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DESCRIPTION_COD_ACT</v>
+        <v>DATE</v>
       </c>
       <c r="B11" t="str">
         <v>Sí</v>
       </c>
       <c r="C11" t="str">
-        <v>Motivo o tipificación.</v>
+        <v>Fecha de la conversación (en el export viene con la hora).</v>
       </c>
       <c r="D11" t="str">
-        <v>Agendamiento</v>
+        <v>2026-09-01</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -553,24 +548,58 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>NOMBRE DE SKILL</v>
+        <v>DESCRIPTION_COD_ACT</v>
       </c>
       <c r="B12" t="str">
         <v>Sí</v>
       </c>
       <c r="C12" t="str">
-        <v>Cola de WhatsApp ("NOMBRE DE SKILL" en el export).</v>
+        <v>Motivo o tipificación.</v>
       </c>
       <c r="D12" t="str">
-        <v>WHATSAPP GENERAL</v>
+        <v>Agendamiento</v>
       </c>
       <c r="E12" t="str">
-        <v>SKILL_NAME</v>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SKILL_ID</v>
+      </c>
+      <c r="B13" t="str">
+        <v>No</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Número del skill (ver la tabla de skills). 0 = WhatsApp de salida.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>4327</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CHANNEL</v>
+      </c>
+      <c r="B14" t="str">
+        <v>No</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Canal del chat ("whatsapp").</v>
+      </c>
+      <c r="D14" t="str">
+        <v>whatsapp</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
+++ b/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
@@ -398,42 +398,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:AF1"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="29.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="15.83203125" customWidth="1"/>
+    <col min="16" max="16" width="15.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="21.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="15.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="21.83203125" customWidth="1"/>
+    <col min="25" max="25" width="28.83203125" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" customWidth="1"/>
+    <col min="27" max="27" width="14.83203125" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" customWidth="1"/>
+    <col min="30" max="30" width="14.83203125" customWidth="1"/>
+    <col min="31" max="31" width="15.83203125" customWidth="1"/>
+    <col min="32" max="32" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>CONN_ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>CHANNEL</v>
+      </c>
+      <c r="C1" t="str">
+        <v>DATE</v>
+      </c>
+      <c r="D1" t="str">
+        <v>DATE_CLOSE</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ROUTING</v>
+      </c>
+      <c r="F1" t="str">
+        <v>CUSTOMER_NAME</v>
+      </c>
+      <c r="G1" t="str">
+        <v>CUSTOMER_EMAIL</v>
+      </c>
+      <c r="H1" t="str">
+        <v>CUSTOMER_PHONE</v>
+      </c>
+      <c r="I1" t="str">
+        <v>CUSTOMER_CHARS</v>
+      </c>
+      <c r="J1" t="str">
+        <v>ASSIGNMENT_TIME</v>
+      </c>
+      <c r="K1" t="str">
+        <v>AGENT_AVERAGE_RESPONSE_TIME</v>
+      </c>
+      <c r="L1" t="str">
+        <v>AGENT_ID</v>
+      </c>
+      <c r="M1" t="str">
         <v>AGENT_NAME</v>
       </c>
-      <c r="B1" t="str">
-        <v>DATE</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="N1" t="str">
+        <v>AGENT_CHARS</v>
+      </c>
+      <c r="O1" t="str">
+        <v>TIME_ON_AGENT</v>
+      </c>
+      <c r="P1" t="str">
+        <v>CHAT_DURATION</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>COD_ACT</v>
+      </c>
+      <c r="R1" t="str">
         <v>DESCRIPTION_COD_ACT</v>
       </c>
-      <c r="D1" t="str">
+      <c r="S1" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="T1" t="str">
+        <v>TRANSFER_TYPE</v>
+      </c>
+      <c r="U1" t="str">
+        <v>COMMENTS</v>
+      </c>
+      <c r="V1" t="str">
+        <v>CUSTOMER_ID</v>
+      </c>
+      <c r="W1" t="str">
         <v>SKILL_ID</v>
       </c>
-      <c r="E1" t="str">
-        <v>CHANNEL</v>
+      <c r="X1" t="str">
+        <v>FIRST RESPONSE TIME</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>LAST_PARTICIPANT_WHO_SPOKE</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>EXTRA_FIELD</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>COMMENT</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>USER_ID</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>FEELING</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>AGENT_DNI</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>AGENT_ANSWERS</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>BSUID</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E41"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -514,16 +622,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AGENT_NAME</v>
+        <v>CONN_ID</v>
       </c>
       <c r="B10" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
       <c r="C10" t="str">
-        <v>Asesor.</v>
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
       </c>
       <c r="D10" t="str">
-        <v>Asesor Ejemplo Uno</v>
+        <v>EJEMPLO-0001</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -531,16 +639,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DATE</v>
+        <v>CHANNEL</v>
       </c>
       <c r="B11" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
       <c r="C11" t="str">
-        <v>Fecha de la conversación (en el export viene con la hora).</v>
+        <v>Canal del chat ("whatsapp").</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-09-01</v>
+        <v>whatsapp</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -548,16 +656,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>DESCRIPTION_COD_ACT</v>
+        <v>DATE</v>
       </c>
       <c r="B12" t="str">
         <v>Sí</v>
       </c>
       <c r="C12" t="str">
-        <v>Motivo o tipificación.</v>
+        <v>Fecha y hora de la conversación.</v>
       </c>
       <c r="D12" t="str">
-        <v>Agendamiento</v>
+        <v>2026-09-01 08:15:00</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -565,16 +673,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SKILL_ID</v>
+        <v>DATE_CLOSE</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
       </c>
       <c r="C13" t="str">
-        <v>Número del skill (ver la tabla de skills). 0 = WhatsApp de salida.</v>
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
       </c>
       <c r="D13" t="str">
-        <v>4327</v>
+        <v>2026-09-01 08:30:00</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -582,24 +690,483 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CHANNEL</v>
+        <v>ROUTING</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
       </c>
       <c r="C14" t="str">
-        <v>Canal del chat ("whatsapp").</v>
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
       </c>
       <c r="D14" t="str">
-        <v>whatsapp</v>
+        <v>-</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CUSTOMER_NAME</v>
+      </c>
+      <c r="B15" t="str">
+        <v>No</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Cliente Ejemplo</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CUSTOMER_EMAIL</v>
+      </c>
+      <c r="B16" t="str">
+        <v>No</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>cliente@ejemplo.com</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CUSTOMER_PHONE</v>
+      </c>
+      <c r="B17" t="str">
+        <v>No</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>3000000001</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CUSTOMER_CHARS</v>
+      </c>
+      <c r="B18" t="str">
+        <v>No</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ASSIGNMENT_TIME</v>
+      </c>
+      <c r="B19" t="str">
+        <v>No</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AGENT_AVERAGE_RESPONSE_TIME</v>
+      </c>
+      <c r="B20" t="str">
+        <v>No</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AGENT_ID</v>
+      </c>
+      <c r="B21" t="str">
+        <v>No</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>0000</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>AGENT_NAME</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Asesor.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Asesor Ejemplo Uno</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>AGENT_CHARS</v>
+      </c>
+      <c r="B23" t="str">
+        <v>No</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TIME_ON_AGENT</v>
+      </c>
+      <c r="B24" t="str">
+        <v>No</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CHAT_DURATION</v>
+      </c>
+      <c r="B25" t="str">
+        <v>No</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>COD_ACT</v>
+      </c>
+      <c r="B26" t="str">
+        <v>No</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>401</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>DESCRIPTION_COD_ACT</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Motivo o tipificación.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Agendamiento</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="B28" t="str">
+        <v>No</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>-</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TRANSFER_TYPE</v>
+      </c>
+      <c r="B29" t="str">
+        <v>No</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>-</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>COMMENTS</v>
+      </c>
+      <c r="B30" t="str">
+        <v>No</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CUSTOMER_ID</v>
+      </c>
+      <c r="B31" t="str">
+        <v>No</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>1000000001</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SKILL_ID</v>
+      </c>
+      <c r="B32" t="str">
+        <v>No</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Número del skill (ver la tabla de skills). 0 = WhatsApp de salida.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>4327</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>FIRST RESPONSE TIME</v>
+      </c>
+      <c r="B33" t="str">
+        <v>No</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>LAST_PARTICIPANT_WHO_SPOKE</v>
+      </c>
+      <c r="B34" t="str">
+        <v>No</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>-</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>EXTRA_FIELD</v>
+      </c>
+      <c r="B35" t="str">
+        <v>No</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>COMMENT</v>
+      </c>
+      <c r="B36" t="str">
+        <v>No</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>USER_ID</v>
+      </c>
+      <c r="B37" t="str">
+        <v>No</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>0000</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>FEELING</v>
+      </c>
+      <c r="B38" t="str">
+        <v>No</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>-</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>AGENT_DNI</v>
+      </c>
+      <c r="B39" t="str">
+        <v>No</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>0000</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>AGENT_ANSWERS</v>
+      </c>
+      <c r="B40" t="str">
+        <v>No</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>BSUID</v>
+      </c>
+      <c r="B41" t="str">
+        <v>No</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Viene en el export de Wolkvox; el sistema nunca la lee ni la guarda.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>-</v>
+      </c>
+      <c r="E41" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
+++ b/server/plantillas/PLANTILLA_TIPIFICACION_WHATSAPP.xlsx
@@ -560,7 +560,7 @@
         <v>De dónde sale</v>
       </c>
       <c r="B2" t="str">
-        <v>Wolkvox: CDR de WhatsApp, export "HistChat&lt;fecha&gt;" — [ruta pendiente de confirmar con Edwin]. Se sube tal cual (no hay que renombrar la hoja); el sistema nunca lee nombres, correos, teléfonos ni el texto de las conversaciones. Un SKILL_ID que no esté en la tabla de skills se ignora y la vista previa dice cuántos.</v>
+        <v>Wolkvox: CDR de WhatsApp, export "HistChat&lt;fecha&gt;" — [ruta pendiente de confirmar con Edwin]. Se sube tal cual (no hay que renombrar la hoja); el sistema nunca lee nombres, correos, teléfonos ni el texto de las conversaciones. Un SKILL_ID que no esté en la tabla de skills se guarda como "Skill &lt;número&gt;" y la vista previa dice cuántos. El día de cada chat sale de DATE_CLOSE (fecha de cierre).</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         <v>Sí</v>
       </c>
       <c r="C12" t="str">
-        <v>Fecha y hora de la conversación.</v>
+        <v>Fecha y hora de apertura del chat. Solo se usa si la fila no trae DATE_CLOSE.</v>
       </c>
       <c r="D12" t="str">
         <v>2026-09-01 08:15:00</v>
@@ -679,7 +679,7 @@
         <v>No</v>
       </c>
       <c r="C13" t="str">
-        <v>Viene en el export de Wolkvox; el sistema no la usa.</v>
+        <v>Fecha y hora de cierre: define el día y el mes del chat (Wolkvox arma el archivo por fecha de cierre).</v>
       </c>
       <c r="D13" t="str">
         <v>2026-09-01 08:30:00</v>
